--- a/artfynd/A 56250-2021 artfynd.xlsx
+++ b/artfynd/A 56250-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56250-2021 artfynd.xlsx
+++ b/artfynd/A 56250-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101708500</v>
+        <v>101708479</v>
       </c>
       <c r="B2" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>219711</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545837.3641339884</v>
+        <v>545789</v>
       </c>
       <c r="R2" t="n">
-        <v>6455257.58715764</v>
+        <v>6455196</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,19 +743,9 @@
           <t>2022-06-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +769,431 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Linköpings kommuns naturvårdsprogram 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100681800</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stora Mörken (mot S), Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>545809</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6455194</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-05-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-05-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Dike</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bengt Westman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bengt Westman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>101708556</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kulla, Vårdnäs, Linköpings kommun, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>545829</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6455256</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-06-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-06-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Ek</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>David Ek</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Linköpings kommuns naturvårdsprogram 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130789874</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stora Mörken S, Skams backe V, sänkan, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>545830</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6455274</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1989-07-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1989-07-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minsta antal. Många fertila.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bäckdal.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>101708500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kulla, Vårdnäs, Linköpings kommun, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>545838</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6455258</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vårdnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-06-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-06-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Ek</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>David Ek</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>

--- a/artfynd/A 56250-2021 artfynd.xlsx
+++ b/artfynd/A 56250-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101708479</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100681800</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101708556</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130789874</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,8 +1223,20 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101708500</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>